--- a/data/nzd0057/nzd0057.xlsx
+++ b/data/nzd0057/nzd0057.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D306"/>
+  <dimension ref="A1:D307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5938,6 +5938,24 @@
         <v>337.91</v>
       </c>
       <c r="D306" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>348.88</v>
+      </c>
+      <c r="C307" t="n">
+        <v>337.84</v>
+      </c>
+      <c r="D307" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5954,7 +5972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9537,6 +9555,16 @@
       </c>
       <c r="B358" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -9705,28 +9733,28 @@
         <v>0.1001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09388141743199173</v>
+        <v>0.09228390392223045</v>
       </c>
       <c r="J2" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K2" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03775302478603604</v>
+        <v>0.03673453149699524</v>
       </c>
       <c r="M2" t="n">
-        <v>2.876829162686484</v>
+        <v>2.874542000009776</v>
       </c>
       <c r="N2" t="n">
-        <v>12.15881373686121</v>
+        <v>12.13763112323533</v>
       </c>
       <c r="O2" t="n">
-        <v>3.486949058541178</v>
+        <v>3.483910320779702</v>
       </c>
       <c r="P2" t="n">
-        <v>348.8059197181138</v>
+        <v>348.822360657097</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9783,28 +9811,28 @@
         <v>0.1118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0970137222574597</v>
+        <v>0.0921614267110836</v>
       </c>
       <c r="J3" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K3" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03003890737316561</v>
+        <v>0.02711125681442095</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3036835514609</v>
+        <v>3.315072636557119</v>
       </c>
       <c r="N3" t="n">
-        <v>16.44877827888364</v>
+        <v>16.5661823476178</v>
       </c>
       <c r="O3" t="n">
-        <v>4.055709343491425</v>
+        <v>4.070157533513636</v>
       </c>
       <c r="P3" t="n">
-        <v>342.561786974796</v>
+        <v>342.6117247653179</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9842,7 +9870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D306"/>
+  <dimension ref="A1:D307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16577,6 +16605,28 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>-35.12171478233812,174.01208912422777</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>-35.1215842565192,174.01298217976628</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0057/nzd0057.xlsx
+++ b/data/nzd0057/nzd0057.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D307"/>
+  <dimension ref="A1:D310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5956,6 +5956,60 @@
         <v>337.84</v>
       </c>
       <c r="D307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>347.59</v>
+      </c>
+      <c r="C308" t="n">
+        <v>337.74</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="C309" t="n">
+        <v>338.79</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>345.89</v>
+      </c>
+      <c r="C310" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="D310" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5972,7 +6026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9565,6 +9619,36 @@
       </c>
       <c r="B359" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -9733,28 +9817,28 @@
         <v>0.1001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09228390392223045</v>
+        <v>0.08423996473369461</v>
       </c>
       <c r="J2" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K2" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03673453149699524</v>
+        <v>0.03104728638403864</v>
       </c>
       <c r="M2" t="n">
-        <v>2.874542000009776</v>
+        <v>2.882384576662327</v>
       </c>
       <c r="N2" t="n">
-        <v>12.13763112323533</v>
+        <v>12.18680047592411</v>
       </c>
       <c r="O2" t="n">
-        <v>3.483910320779702</v>
+        <v>3.490959821585478</v>
       </c>
       <c r="P2" t="n">
-        <v>348.822360657097</v>
+        <v>348.9054989397864</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9811,28 +9895,28 @@
         <v>0.1118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0921614267110836</v>
+        <v>0.0795310802822258</v>
       </c>
       <c r="J3" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K3" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02711125681442095</v>
+        <v>0.02029488134318436</v>
       </c>
       <c r="M3" t="n">
-        <v>3.315072636557119</v>
+        <v>3.341220060110458</v>
       </c>
       <c r="N3" t="n">
-        <v>16.5661823476178</v>
+        <v>16.80184740988467</v>
       </c>
       <c r="O3" t="n">
-        <v>4.070157533513636</v>
+        <v>4.099005661118885</v>
       </c>
       <c r="P3" t="n">
-        <v>342.6117247653179</v>
+        <v>342.7422228864667</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9870,7 +9954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D307"/>
+  <dimension ref="A1:D310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16627,6 +16711,72 @@
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>-35.121725828902186,174.01209355534803</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>-35.12158511284017,174.0129825232695</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-35.12172274614014,174.0120923187562</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-35.12157612146972,174.01297891648608</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-35.12174038638944,174.01209939481072</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-35.12157261055358,174.01297750812324</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0057/nzd0057.xlsx
+++ b/data/nzd0057/nzd0057.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D310"/>
+  <dimension ref="A1:D312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6010,6 +6010,42 @@
         <v>339.2</v>
       </c>
       <c r="D310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>345.71</v>
+      </c>
+      <c r="C311" t="n">
+        <v>342.18</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>345.77</v>
+      </c>
+      <c r="C312" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="D312" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6026,7 +6062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B362"/>
+  <dimension ref="A1:B364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9649,6 +9685,26 @@
       </c>
       <c r="B362" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -9817,28 +9873,28 @@
         <v>0.1001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08423996473369461</v>
+        <v>0.07721001674292007</v>
       </c>
       <c r="J2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03104728638403864</v>
+        <v>0.02620545365744031</v>
       </c>
       <c r="M2" t="n">
-        <v>2.882384576662327</v>
+        <v>2.895342394928645</v>
       </c>
       <c r="N2" t="n">
-        <v>12.18680047592411</v>
+        <v>12.29218583750584</v>
       </c>
       <c r="O2" t="n">
-        <v>3.490959821585478</v>
+        <v>3.506021368660757</v>
       </c>
       <c r="P2" t="n">
-        <v>348.9054989397864</v>
+        <v>348.9788280678735</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9895,28 +9951,28 @@
         <v>0.1118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0795310802822258</v>
+        <v>0.07545820325495629</v>
       </c>
       <c r="J3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02029488134318436</v>
+        <v>0.0185062021820489</v>
       </c>
       <c r="M3" t="n">
-        <v>3.341220060110458</v>
+        <v>3.338585409554998</v>
       </c>
       <c r="N3" t="n">
-        <v>16.80184740988467</v>
+        <v>16.75673283861842</v>
       </c>
       <c r="O3" t="n">
-        <v>4.099005661118885</v>
+        <v>4.093498850447917</v>
       </c>
       <c r="P3" t="n">
-        <v>342.7422228864667</v>
+        <v>342.7847157199458</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9954,7 +10010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D310"/>
+  <dimension ref="A1:D312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16777,6 +16833,50 @@
         </is>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-35.12174192777042,174.0121000131069</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-35.121547092187015,174.01296727173371</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-35.12174141397675,174.01209980700818</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-35.12155479907637,174.01297036326005</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0057/nzd0057.xlsx
+++ b/data/nzd0057/nzd0057.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D312"/>
+  <dimension ref="A1:D314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6046,6 +6046,42 @@
         <v>341.28</v>
       </c>
       <c r="D312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>345.49</v>
+      </c>
+      <c r="C313" t="n">
+        <v>341.57</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="C314" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="D314" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6062,7 +6098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B364"/>
+  <dimension ref="A1:B366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9705,6 +9741,26 @@
       </c>
       <c r="B364" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -9873,28 +9929,28 @@
         <v>0.1001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07721001674292007</v>
+        <v>0.07023518043574983</v>
       </c>
       <c r="J2" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K2" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02620545365744031</v>
+        <v>0.02177764803874627</v>
       </c>
       <c r="M2" t="n">
-        <v>2.895342394928645</v>
+        <v>2.908095096552651</v>
       </c>
       <c r="N2" t="n">
-        <v>12.29218583750584</v>
+        <v>12.39764782964142</v>
       </c>
       <c r="O2" t="n">
-        <v>3.506021368660757</v>
+        <v>3.521029370743934</v>
       </c>
       <c r="P2" t="n">
-        <v>348.9788280678735</v>
+        <v>349.0519150225285</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9951,28 +10007,28 @@
         <v>0.1118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07545820325495629</v>
+        <v>0.07112968070094822</v>
       </c>
       <c r="J3" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K3" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0185062021820489</v>
+        <v>0.01664800239025788</v>
       </c>
       <c r="M3" t="n">
-        <v>3.338585409554998</v>
+        <v>3.337033123657407</v>
       </c>
       <c r="N3" t="n">
-        <v>16.75673283861842</v>
+        <v>16.72060072240476</v>
       </c>
       <c r="O3" t="n">
-        <v>4.093498850447917</v>
+        <v>4.089083115125536</v>
       </c>
       <c r="P3" t="n">
-        <v>342.7847157199458</v>
+        <v>342.8300741931232</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10010,7 +10066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D312"/>
+  <dimension ref="A1:D314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16877,6 +16933,50 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-35.121743811680496,174.01210076880227</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-35.12155231574536,174.0129693671015</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-35.1217415852413,174.01209987570778</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>-35.121554627812166,174.01297029455947</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0057/nzd0057.xlsx
+++ b/data/nzd0057/nzd0057.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6082,6 +6082,60 @@
         <v>341.3</v>
       </c>
       <c r="D314" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>344.54</v>
+      </c>
+      <c r="C315" t="n">
+        <v>339.02</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>345.09</v>
+      </c>
+      <c r="C316" t="n">
+        <v>338.97</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>345.43</v>
+      </c>
+      <c r="C317" t="n">
+        <v>339.44</v>
+      </c>
+      <c r="D317" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6098,7 +6152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9761,6 +9815,36 @@
       </c>
       <c r="B366" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -9929,28 +10013,28 @@
         <v>0.1001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07023518043574983</v>
+        <v>0.05909959434820432</v>
       </c>
       <c r="J2" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K2" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02177764803874627</v>
+        <v>0.01545147705548866</v>
       </c>
       <c r="M2" t="n">
-        <v>2.908095096552651</v>
+        <v>2.930615902315269</v>
       </c>
       <c r="N2" t="n">
-        <v>12.39764782964142</v>
+        <v>12.6029930839144</v>
       </c>
       <c r="O2" t="n">
-        <v>3.521029370743934</v>
+        <v>3.550069447759354</v>
       </c>
       <c r="P2" t="n">
-        <v>349.0519150225285</v>
+        <v>349.1689707200727</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10007,28 +10091,28 @@
         <v>0.1118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07112968070094822</v>
+        <v>0.06060231145251603</v>
       </c>
       <c r="J3" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K3" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01664800239025788</v>
+        <v>0.01219248188121458</v>
       </c>
       <c r="M3" t="n">
-        <v>3.337033123657407</v>
+        <v>3.353182552990411</v>
       </c>
       <c r="N3" t="n">
-        <v>16.72060072240476</v>
+        <v>16.84985472392869</v>
       </c>
       <c r="O3" t="n">
-        <v>4.089083115125536</v>
+        <v>4.104857454763648</v>
       </c>
       <c r="P3" t="n">
-        <v>342.8300741931232</v>
+        <v>342.9407389804362</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10066,7 +10150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16977,6 +17061,72 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-35.121751946746706,174.01210403203262</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>-35.1215741519314,174.01297812642883</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-35.121747236971544,174.0121021427939</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-35.12157458009191,174.01297829818043</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-35.12174432547416,174.012100974901</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-35.12157055538317,174.01297668371578</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
